--- a/QA_Documentation/Test_Cases.xlsx
+++ b/QA_Documentation/Test_Cases.xlsx
@@ -478,18 +478,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,37 +509,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Linked Bug ID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Executed By</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
         </is>
       </c>
     </row>
@@ -552,35 +576,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>API server is running; database is empty</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Create employee with valid data</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>POST /employees with valid name, email, leave_balance</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>name=Aman Verma, email=aman@test.com, balance=20</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>201/200 response; employee created with given balance</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Employee created successfully with id=1</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -595,37 +639,57 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>An employee with email aman@test.com already exists</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Create employee with an email already in use</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>POST /employees using an email that already exists</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>email=aman@test.com (duplicate)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>400 response with a clear 'email already exists' message</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>500 Internal Server Error (unhandled DB constraint error)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>BUG-01</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -642,35 +706,55 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Employee id=1 exists with balance=20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Submit a valid leave request</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>POST /leave-requests with a 5-day range</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>start=2026-10-01, end=2026-10-05</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Request created with status PENDING</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Request created, status PENDING</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -685,37 +769,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Employee id=1 exists</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Submit request with end date before start date</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>POST /leave-requests with an inverted date range</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>start=2026-10-10, end=2026-10-05</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>400 validation error; request rejected</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Request accepted and stored as PENDING</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>BUG-02</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -732,35 +836,55 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No employee exists with id=999</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Submit leave request for a non-existent employee</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>POST /leave-requests with an invalid employee_id</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>employee_id=999</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>404 'Employee not found'</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>404 'Employee not found'</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -775,35 +899,55 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Employee id=1 exists with balance=20, no approvals yet</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Fetch leave balance before any approval</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>GET /employees/{id}</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>employee_id=1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Returns unchanged starting balance (20)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Returned balance=20</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -818,35 +962,55 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Leave request id=1 exists with status=PENDING</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Approve a pending leave request</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>PUT /leave-requests/{id}/approve</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>request id=1 (5-day request)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Status -&gt; APPROVED; balance reduced by 5 (20-&gt;15)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Status APPROVED; balance 20-&gt;15</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -861,37 +1025,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Leave request id=1 already has status=APPROVED</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Re-approve an already-approved leave request</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Call approve again on the same request id</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>request id=1 (already APPROVED)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>400 error; request already processed, no further deduction</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Approved again; balance deducted a 2nd time (15-&gt;10)</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>BUG-03</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -908,37 +1092,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Employee has ~10 days remaining balance</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Approve a request that exceeds remaining balance</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Approve a 30-day request when ~10 days remain</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>request covering 2026-11-01 to 2026-11-30</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>400 error; 'insufficient leave balance'</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Approved anyway; balance went negative (10-&gt;-20)</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>BUG-04</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -955,37 +1159,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Leave request id=1 has status=REJECTED</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>Approve a request that was already REJECTED</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Reject a request, then call approve on the same id</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>request id=1</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>400 error; cannot approve a rejected request</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Request approved successfully; balance deducted</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>BUG-03</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1002,37 +1226,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>A request for 2026-10-01 to 2026-10-05 already exists for employee id=1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>Submit a duplicate/overlapping request</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>POST a request with identical dates to an existing one, same employee</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>start=2026-10-01, end=2026-10-05 (duplicate of TC-03)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>400/409 error, or flagged as overlapping</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Duplicate request accepted with no warning</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>BUG-05</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1049,35 +1293,55 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Leave request id=1 exists with status=PENDING</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Reject a pending leave request</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>PUT /leave-requests/{id}/reject</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>request id=1 (PENDING)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Status -&gt; REJECTED; leave balance unaffected</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Status REJECTED; balance unchanged</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1092,35 +1356,55 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No employee exists with id=999</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Fetch a non-existent employee</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>GET /employees/999</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>employee_id=999</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>404 'Employee not found'</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>404 'Employee not found'</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1135,35 +1419,55 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No leave request exists with id=999</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>Fetch a non-existent leave request</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>GET /leave-requests/999</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>request_id=999</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>404 'Leave request not found'</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>404 'Leave request not found'</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1176,18 +1480,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1203,37 +1511,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Linked Bug ID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Executed By</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
         </is>
       </c>
     </row>
@@ -1250,39 +1578,51 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-01 has been fixed</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Re-test: duplicate email handling after fix</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>POST /employees with a duplicate email</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>email=aman@test.com</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>400 with clear validation message</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Not executed - pending BUG-01 fix</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>BUG-01</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1297,39 +1637,51 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-02 has been fixed</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Re-test: inverted date range after fix</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>POST /leave-requests with end date before start date</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>start=2026-10-10, end=2026-10-05</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>400 validation error</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Not executed - pending BUG-02 fix</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>BUG-02</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1344,39 +1696,51 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-03 has been fixed</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Re-test: status guard on approve after fix</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Approve an already-approved and an already-rejected request</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>request id in APPROVED / REJECTED state</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>400 error in both cases; no balance change</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Not executed - pending BUG-03 fix</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>BUG-03</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1391,39 +1755,51 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>BUG-04 has been fixed</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Re-test: balance validation on approve after fix</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Approve a request exceeding remaining balance</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>30-day request, ~10 days remaining</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>400 'insufficient leave balance'</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Not executed - pending BUG-04 fix</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>BUG-04</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1438,39 +1814,51 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>BUG-05 has been fixed</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Re-test: overlap/duplicate detection after fix</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Submit a request duplicating an existing one</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>same employee, same date range</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>400/409 duplicate/overlap error</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Not executed - pending BUG-05 fix</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>BUG-05</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1485,35 +1873,55 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>API server is running; database is empty</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Confirm valid employee creation still works</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>POST /employees with valid data</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>name/email/balance</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Employee created as before</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Pass (unaffected by fixes)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1528,35 +1936,55 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Leave request id=1 exists with status=PENDING</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Confirm normal single-approve flow still works</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Approve one pending request once</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>request id=1</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Status APPROVED, balance deducted once</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Pass (unaffected by fixes)</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1569,18 +1997,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1596,37 +2028,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Linked Bug ID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Executed By</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
         </is>
       </c>
     </row>
@@ -1643,35 +2095,55 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Code has been deployed/built</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>API server starts successfully</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Run uvicorn main:app and check /docs loads</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Server responds 200 on /docs</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Server up, /docs returned 200</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1686,35 +2158,55 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Database is reachable</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Create an employee (core path)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>POST /employees with minimal valid payload</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>name, email</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Employee created, id returned</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Employee created, id=1</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1729,35 +2221,55 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Employee id=1 exists</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Submit a leave request (core path)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>POST /leave-requests with valid dates</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>employee_id=1, valid date range</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Request created, status PENDING</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Request created, status PENDING</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1772,35 +2284,55 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A PENDING leave request exists</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Approve a leave request (core path)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PUT /leave-requests/{id}/approve</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>a fresh PENDING request</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Status APPROVED, balance updated</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Status APPROVED, balance updated</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1815,35 +2347,55 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Employee id=1 exists</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Fetch employee record (core path)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>GET /employees/{id}</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>employee_id=1</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Employee record returned</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Employee record returned</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QA_Documentation/Test_Cases.xlsx
+++ b/QA_Documentation/Test_Cases.xlsx
@@ -1608,12 +1608,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Not executed - pending BUG-01 fix</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Retested after fix - returns 400 'Email already registered'</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1621,8 +1621,16 @@
           <t>BUG-01</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1667,12 +1675,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not executed - pending BUG-02 fix</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Retested after fix - returns 400 'end_date must be on or after start_date'</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1680,8 +1688,16 @@
           <t>BUG-02</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1726,12 +1742,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not executed - pending BUG-03 fix</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Retested after fix - approve/reject on non-PENDING now returns 400 in both cases</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1739,8 +1755,16 @@
           <t>BUG-03</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,12 +1809,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Not executed - pending BUG-04 fix</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Retested after fix - returns 400 'Insufficient leave balance'</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1798,8 +1822,16 @@
           <t>BUG-04</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1844,12 +1876,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not executed - pending BUG-05 fix</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Retested after fix - returns 409 with conflicting request ID</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1857,8 +1889,16 @@
           <t>BUG-05</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Tanisha</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
